--- a/신고신저가_20260826.xlsx
+++ b/신고신저가_20260826.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,74 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 8월 25일은 지수가 셋 다 오르는 동안 그 아래에서 돈이 완전히 다른 곳으로 옮겨간 하루였다. 전날까지 AI 하드웨어를 팔던 자금이 오늘은 헬스케어와 금광, 은행으로 들어가 미국 신고가의 대부분을 채웠고, 신저가는 AI 체인이 아니라 집을 짓고 고치는 회사들, 그러니까 공조와 통신망 시공, 건자재에 몰렸다. 실적으로 이익을 증명한 종목만 사고 실물 수요가 식은 쪽은 무차별로 던지는 장세로 추정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/25): 지수만 보면 반등이지만 안을 열면 헬스케어와 금이 시장을 통째로 가져간 날이다. 나스닥이 0.66퍼센트 오른 가운데 신고가 64종 중 헬스케어가 14종, 금·구리 광산이 13종으로 절반 가까이를 차지했다. 머크가 흑색종 백신 3상 결과로 3.84퍼센트 올라 신고가에 올라섰고 화이자와 버텍스, 바이오젠이 뒤를 따랐는데, 헬스케어 업종의 선행 주가수익배수가 20배로 후행 34배의 절반 수준이라 이익 회복을 미리 사는 자리로 보인다. 신저가 26종은 성격이 전혀 다르다. 왓스코와 캐리어, 레녹스가 공조에서 나란히 떨어졌고 다이컴과 마스텍이 통신망 시공에서, 암라이즈가 건자재에서 밀렸다. 딕스스포팅굿즈는 2분기 실적과 가이던스를 함께 낮추며 30.68퍼센트 폭락했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/25): 사흘 만의 반등이었고 오른 자리는 소재와 기계였다. 닛케이225가 328엔, 0.50퍼센트 올라 65,856엔에 마쳤고 철강·비철 상장지수펀드가 2.5퍼센트, 기계가 2.0퍼센트로 앞장섰다. 신고가는 11종이 나온 반면 신저가는 두 종에 그쳤다. 소프트뱅크가 통신주 동반 강세를 타고 올라섰고, 간사이전력은 기업용 전기요금 인상 발표 이후의 수익성 개선 기대를 이어갔다. 반대편의 패스트리테일링은 개별 악재 없이 지수 기여 상위주가 차익실현에 눌린 경우다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/25): 지수는 멈춰 섰지만 안에서는 바이오와 전기차가 정반대로 갈렸다. 항셍지수가 0.02퍼센트 내려 사실상 보합이었는데, 우시XDC가 가이던스 상향과 수주잔고 급증으로 14.83퍼센트 뛰며 우시바이오로직스까지 함께 끌어올렸다. 같은 날 샤오펑은 2분기 인도량 증가율이 0.1퍼센트에 그쳐 9.19퍼센트 급락했고 니오도 3.45퍼센트 밀려 소비내구재가 약세로 돌아섰다. 위탁생산은 수주가 곧 이익이고 전기차는 인도량이 곧 이익이라, 둘 다 물량 숫자 하나로 판정받은 셈이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/25): 대형주가 쉬고 소형주만 버티는, 힘이 빠진 장이었다. 상해종합이 0.19퍼센트 오르는 동안 CSI300은 0.24퍼센트 내려 방향이 갈렸고, 신고가 4종에 신저가 10종으로 신저가가 두 배 넘게 많았다. 전자기술에서만 신저가가 4종 나왔는데 반도체 상장지수펀드가 한 주 사이 11퍼센트 빠진 흐름의 연장이다. 당일에는 부동산과 의약이 1.9퍼센트씩 오르며 자리를 바꿨을 뿐 새로 들어온 돈의 흔적은 보이지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 8월 26일 장 마감 후 나오는 다이컴 실적을 본다. 통신망 시공 수주가 버티는지가 AI 데이터센터 건설이 실제로 돌아가고 있는지를 가리는 첫 숫자다. ② 헬스케어의 선행 배수 20배가 실적으로 채워지는지 확인한다. 지금 사는 것은 이익이 아니라 이익이 올 것이라는 기대이므로, 다음 분기 가이던스가 어긋나면 되돌림이 빠르다. ③ 중국A 반도체가 한 주 11퍼센트 하락을 멈추는지 본다. 홍콩 항셍테크가 연초 대비 16.5퍼센트 마이너스로 홍콩 세 지수 중 꼴찌인 것과 같은 뿌리다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 이날 공조 세 종목이 함께 신저가로 떨어졌는데, 왓스코와 캐리어·레녹스는 같은 날 같은 방향으로 움직였어도 깎인 것이 서로 다르다. 왓스코는 장비를 만들지 않고 설치업자에게 파는 유통이다. 7월 말 2분기 실적에서 매출은 2퍼센트 늘었는데 총이익이 오히려 줄고 주당순이익이 12퍼센트 감소했다. 이는 물량이 늘지 않은 채 가격만 명목으로 붙었고 그 가격조차 할인으로 지켜야 했다는 뜻이라, 이익의 Q와 마진이 함께 깎인 것이다. 반면 캐리어와 레녹스는 아직 그런 숫자를 발표하지 않았다. 유통 창고에서 장비가 안 빠지면 다음 분기 제조사 주문이 줄어들기 때문에, 시장은 왓스코의 실적을 제조사의 선행지표로 읽고 이익이 나오기도 전에 멀티플부터 낮춘 것이다. 하나는 이미 확정된 이익이 깎였고 다른 하나는 아직 오지 않은 이익의 값이 깎였다. 캐리어를 데이터센터 냉각 수혜주로 부르는 시각이 있지만 이날 이긴 것은 주택 교체 사이클이었고, 노출도가 큰 쪽이 서사가 좋은 쪽을 누른다는 점도 함께 확인됐다. 어느 설명이 맞았는지는 캐리어와 레녹스의 다음 분기 수주잔고와 출하량이 채점해 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +781,19 @@
       <c r="C2" t="n">
         <v>7677.28</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>-0.19</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>3.56</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>12.15</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +819,19 @@
       <c r="C3" t="n">
         <v>26151.3</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>-0.53</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>4.89</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>-1.89</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>12.52</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +857,19 @@
       <c r="C4" t="n">
         <v>6696.96</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>-3.12</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-4.03</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-5.64</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-14.31</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>58.92</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +895,19 @@
       <c r="C5" t="n">
         <v>65528.09</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>-0.74</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-5.33</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-1.35</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>30.17</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +933,19 @@
       <c r="C6" t="n">
         <v>3889.44</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>-2.53</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-4.99</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-2</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +971,19 @@
       <c r="C7" t="n">
         <v>4552.03</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.24</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>-3.68</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-7.26</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-1.68</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1009,19 @@
       <c r="C8" t="n">
         <v>25511.1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="5" t="n">
         <v>-0.47</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1047,19 @@
       <c r="C9" t="n">
         <v>4588.54</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="5" t="n">
         <v>-0.12</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>-3.18</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>-2.41</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="5" t="n">
         <v>-7.24</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-16.81</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1178,7 @@
       <c r="F2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1219,7 @@
       <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1260,7 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1301,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1342,7 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1383,7 @@
       <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1424,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1465,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1506,7 @@
       <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1547,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1588,7 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1629,7 @@
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1670,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1711,7 @@
       <c r="F15" t="n">
         <v>-4</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1752,7 @@
       <c r="F16" t="n">
         <v>-5</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1793,7 @@
       <c r="F17" t="n">
         <v>-6</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1996,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2035,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2002,7 +2074,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2043,7 +2115,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2082,7 +2154,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2121,7 +2193,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2162,7 +2234,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2203,7 +2275,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2242,7 +2314,7 @@
       <c r="F30" t="n">
         <v>-1</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2283,7 +2355,7 @@
       <c r="F31" t="n">
         <v>-1</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2677,7 +2749,7 @@
       <c r="F41" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2716,7 +2788,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2755,7 +2827,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2794,7 +2866,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2833,7 +2905,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2874,7 +2946,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2915,7 +2987,7 @@
       <c r="F47" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2954,7 +3026,7 @@
       <c r="F48" t="n">
         <v>-1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2995,7 +3067,7 @@
       <c r="F49" t="n">
         <v>-1</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3036,7 +3108,7 @@
       <c r="F50" t="n">
         <v>-3</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3465,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3432,7 +3504,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3471,7 +3543,7 @@
       <c r="F61" t="n">
         <v>-1</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3510,7 +3582,7 @@
       <c r="F62" t="n">
         <v>-1</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3551,7 +3623,7 @@
       <c r="F63" t="n">
         <v>-2</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3592,7 +3664,7 @@
       <c r="F64" t="n">
         <v>-4</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4173,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4218,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4328,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.9퍼센트 반등했지만 주간으로는 여전히 2.1퍼센트 마이너스다. 연초 대비 26.5퍼센트로 2위 자리는 지키고 있다.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4404,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>3개월 18.6퍼센트로 11개 업종 중 압도적 1위다. 신고가 14종이 나와 로테이션의 종착지 역할을 했다.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4480,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>3개월 12.9퍼센트로 헬스케어 다음이다. 스코샤뱅크 사상최대 순익 등 신고가 10종이 뒷받침했다.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4556,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.3퍼센트 하락. 딕스스포팅굿즈가 가이던스 하향으로 30퍼센트 넘게 빠진 충격이 업종에 남았다.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4632,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.8퍼센트 올랐으나 연초 대비 3.3퍼센트 마이너스로 11개 업종 중 꼴찌다.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4708,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.3퍼센트 하락, 1개월 2.6퍼센트 마이너스다. 통신망 시공과 공조에서 신저가가 쏟아진 여파로 추정한다.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4784,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.1퍼센트 하락으로 11개 업종 중 가장 부진했다. 위험선호 장세에서 방어주가 밀린 자리다.</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4860,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.7퍼센트 하락했지만 연초 대비 40.7퍼센트로 여전히 1위다. 1개월 기준으로도 6.3퍼센트 강세다.</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>40.7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4936,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.2퍼센트 반등. 다만 1개월 5.2퍼센트, 3개월 3.8퍼센트 마이너스로 하락 흐름은 그대로다.</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5012,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>당일은 보합이나 주간 3.5퍼센트로 가장 강했다. 금·구리 광산 신고가 13종이 그대로 반영됐다.</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5088,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.1퍼센트로 사실상 제자리. 1개월 0.9퍼센트 마이너스로 금리 부담을 계속 지고 있다.</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>14.2</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5164,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5236,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5308,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5380,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5452,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5524,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5596,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5668,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5740,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5812,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>9.4</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5884,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>12</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5956,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6028,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6100,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6172,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>44.6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6244,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6316,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6388,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6460,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6532,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-16.5</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6600,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.2퍼센트 하락이지만 주간 11퍼센트, 1개월 10.3퍼센트 급락이다. 연초 1위 자리가 빠르게 반납되고 있다.</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-10.3</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>37.7</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6676,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.2퍼센트 반등에도 주간 9.7퍼센트 마이너스다. 반도체와 함께 기술주 전반이 조정 국면이다.</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6752,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.3퍼센트 올랐으나 3개월 16퍼센트 마이너스다. 통신 설비 투자 기대가 식은 흐름으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-16</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>32.5</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6828,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.3퍼센트 하락. 샤오펑 인도량 부진이 홍콩에서 A주 전기차 심리로 번진 것으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-13.9</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6900,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.5퍼센트 반등에도 연초 대비 20.2퍼센트 마이너스다. 3개월 17.2퍼센트 하락으로 약세가 길다.</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-6.3</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-17.2</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-20.2</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6976,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>3개월 25.2퍼센트 하락으로 13개 중 가장 부진하다. 당일도 0.5퍼센트 밀려 반등 신호가 없다.</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-25.2</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-12.9</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7048,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>연초 대비 21.3퍼센트 마이너스로 13개 중 꼴찌다. 당일 0.2퍼센트 상승은 의미를 두기 어렵다.</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.3</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7124,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.7퍼센트 하락했지만 주간 2.4퍼센트로 유일하게 플러스다. 3개월 7퍼센트로 방어 역할을 하고 있다.</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7200,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>당일 2.7퍼센트 하락으로 13개 중 가장 부진했다. 1개월 6.8퍼센트 상승분을 되돌리는 조정으로 추정한다.</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7276,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.9퍼센트 상승으로 공동 1위다. 다만 3개월 9퍼센트 마이너스라 추세 전환으로 보기는 이르다.</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-9</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>11</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7352,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>당일 보합, 1개월 3.4퍼센트 마이너스다. 거래대금이 살아나야 움직이는 업종인데 그 신호가 없다.</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7428,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>당일 1.9퍼센트 상승, 3개월 12퍼센트로 상위권이다. 마이루이의료 신고가와 같은 방향이다.</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7504,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>당일 0.6퍼센트 상승했으나 연초 대비 16.3퍼센트 마이너스다. 내수 소비 회복 신호는 아직 약하다.</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7572,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-2.7"/>
@@ -7366,7 +7584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-11"/>
@@ -7378,7 +7596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-10.3"/>
@@ -7390,7 +7608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-25.2"/>
@@ -7402,7 +7620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.3"/>
@@ -7414,7 +7632,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7644,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7656,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7668,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7680,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7692,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7806,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7637,10 +7855,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>브로드컴(반도체·AI칩): 마벨의 구글 커스텀칩 수주 확대로 경쟁 우려 지속</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7693,14 +7915,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 비자(카드 결제망): 분기 매출 14% 증가 여진에 피퍼샌들러 목표가 430달러 상향, 3% 급등 신고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7749,19 +7971,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 마스터카드(카드 결제망): 트럼프 투자계좌 6월 매수 공시 부각, 결제 2강 동반 3%대 급등</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7809,10 +8031,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>머크(제약): 흑색종 백신 3상 호재로 종양학 파이프라인 재평가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7865,15 +8091,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7921,10 +8147,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7973,10 +8199,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8025,15 +8251,15 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8081,15 +8307,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>인터랙티브브로커스(온라인 증권사): 특별한 뉴스 없음(고점권 강세 연장)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8133,15 +8363,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8185,15 +8415,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8235,10 +8465,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8291,15 +8521,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>뉴몬트(금광): 금값 온스당 4500달러대 강세, 신규 촉매 없이 상승 연장</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8347,10 +8581,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8403,19 +8637,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 프리포트맥모란(구리 채굴): 구리 강세 지속, 실물자산 선호 흐름</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8463,10 +8697,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>스코샤뱅크(캐나다계 은행): 3분기 순익 사상최대, ROE 목표치 상회</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8515,19 +8753,19 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>(전일) 아그니코이글마인스(금 채굴): 달러 약세와 장기금리 반락으로 금값 급등 수혜</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8571,10 +8809,14 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>스포티파이(음악 스트리밍): 자사주매입 22억달러 확대·구독자 호조</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8623,10 +8865,10 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8675,10 +8917,10 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8727,15 +8969,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8779,15 +9021,19 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>카바나(중고차 온라인 유통): 고베타 위험선호 로테이션, 지분 우려 완화</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8831,10 +9077,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8883,14 +9129,14 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 배릭마이닝(금 채굴): 국제 금값 사상최고 경신에 금광주 일제 신고가</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8939,10 +9185,10 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8991,10 +9237,10 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9039,10 +9285,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9091,15 +9337,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9143,15 +9389,15 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9195,10 +9441,10 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9247,10 +9493,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9303,15 +9549,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9355,15 +9601,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9407,10 +9653,14 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>캐리어글로벌(공조장비 제조): 유통 재고 부진이 제조 주문으로 번질 우려</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9459,10 +9709,10 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9511,14 +9761,14 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>(전일) (금 채굴) 금값 2개월래 최고 4530달러 부근, 금광주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9567,19 +9817,19 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>(전일) (프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9627,15 +9877,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9683,15 +9933,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9735,10 +9985,10 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9791,19 +10041,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9851,10 +10101,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9903,15 +10153,15 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9955,10 +10205,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10011,15 +10261,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10067,15 +10317,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10123,15 +10373,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>암라이즈(건자재·시멘트): 애널리스트 잇단 목표가 하향, 건축외장 부문 약세</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10179,10 +10433,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10231,10 +10485,10 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10283,14 +10537,14 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>(전일) 커티스라이트(방산·원자력 부품): 특별한 뉴스 없음(8월 실적 이후 밸류에이션 조정 지속)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10339,10 +10593,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10391,10 +10645,10 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10443,19 +10697,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="8" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>(전일) 페덱스프레이트(페덱스에서 분할한 소량화물 운송): 화물 업황 약세로 JB헌트와 동반 신저가</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10499,10 +10753,10 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10551,10 +10805,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10603,10 +10857,10 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
+      <c r="N57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10655,15 +10909,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10711,10 +10965,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10763,10 +11017,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10815,10 +11069,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10871,10 +11125,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10923,10 +11177,10 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10973,10 +11227,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11025,10 +11279,10 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11077,15 +11331,15 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11131,15 +11385,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11185,10 +11439,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11237,10 +11491,10 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11293,19 +11547,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="8" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>(전일) BWX테크놀로지스(원자로 부품·소형모듈원전): 개별 악재 없음, AI 전력 테마 되감김에 동반 하락 추정</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11349,10 +11603,10 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11405,10 +11659,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11461,10 +11715,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11513,10 +11767,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11569,14 +11823,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11625,10 +11879,10 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11677,19 +11931,19 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>(전일) (캐나다계 금광 채굴) 금값 3개월래 최고치 랠리와 CIBC 투자의견 상향</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11737,10 +11991,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>왓스코(공조장비 유통): 7월 말 2분기 실적쇼크 여진, 장중 52주 신저 298달러</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11793,10 +12051,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11843,10 +12101,10 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11899,19 +12157,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="8" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>(전일) 인스타카트(온라인 식료품 배달): 개별 뉴스 없음, 광고매출 성장 기대 지속 추정</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11955,15 +12213,15 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12007,10 +12265,10 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12061,10 +12319,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>딕스스포팅굿즈(스포츠용품 유통): 2분기 실적쇼크·가이던스 대폭 하향(풋라커 부진)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12111,15 +12373,15 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12163,15 +12425,19 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>다이컴인더스트리즈(통신망 시공): 8/26 실적 앞둔 차익실현, 개별 악재 없음</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12219,10 +12485,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12275,10 +12541,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12331,14 +12597,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N89" s="8" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>(전일) 페이컴(급여·인사관리 소프트웨어): 신규 촉매 미확인, 소프트웨어 강세에 동반</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12387,10 +12653,10 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12439,7 +12705,7 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N91"/>
@@ -12545,12 +12811,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12592,10 +12858,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>패스트리테일링(유니클로 모기업): 개별 악재 없음, 지수 기여 상위주 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12644,14 +12914,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 이토추상사(종합상사): 3000억엔 자사주매입·사상최대 순이익 모멘텀 지속, 상사 섹터 강세</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12702,19 +12972,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) (일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12760,15 +13030,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>소프트뱅크(통신): NTT·KDDI와 함께 통신주 동반 강세, 연초래 고가권 지속</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12810,10 +13084,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>인펙스(석유·가스 개발): 특별한 뉴스 없음, 유가 강세 흐름 반영한 고가권 잔류</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12864,19 +13142,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (포털·핀테크 플랫폼) 페이페이 결제액 34.9% 성장 등 실적 호조 지속</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12922,10 +13200,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>반다이남코(게임·완구 지식재산): 1분기 영업이익 33퍼센트 증가 서프라이즈 여진</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12978,19 +13260,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) (해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13032,10 +13314,14 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>간사이전력(관서지역 전력): 기업용 전기요금 인상 발표 후 수익성 개선 기대</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13088,14 +13374,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 상선미쓰이(해운 대형사): 신규 재료 없음, 중동 긴장에 따른 운임 상승 기대 지속</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13148,14 +13434,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) (해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13204,19 +13490,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) (증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13258,7 +13544,11 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>니테라(자동차 점화플러그·세라믹): 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N14"/>
@@ -13364,12 +13654,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13415,10 +13705,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>메이디그룹(가전): 특별한 뉴스 없음, 외국계 매수의견 지속에 완만한 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13465,14 +13759,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 시노펙 H주(중국 최대 정유·화학): 상반기 순이익 19% 증가 실적 호조에 5.9% 급등</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13519,10 +13813,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13569,14 +13863,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) (쯔진광업의 금 사업 자회사) 금값 랠리에 모기업 후광 업고 급등</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13629,19 +13923,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) (제약) 상반기 매출 1.9%·조정순이익 12.7% 감소로 업종과 반대로 급락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13685,10 +13979,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>몽타주테크놀로지(메모리 인터페이스 칩): 장중 신저 후 반등 마감, 개별 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13737,19 +14035,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 화훙반도체(중국 2위 파운드리): 알리바바 대규모 유상증자로 AI 투자 자금조달 우려 확산, 동반 급락</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13795,10 +14093,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>우시바이오로직스(바이오의약 위탁생산): 항체약물접합체 호황에 동반 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13841,10 +14143,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13889,10 +14191,10 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13941,10 +14243,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13997,10 +14299,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14051,14 +14353,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이전기 H주(발전설비 제조): 개별 뉴스 없음, 전력설비 섹터 약세 동반 추정</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14109,14 +14411,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 싸이리스그룹(화웨이 협력 전기차 제조): 상반기 순손실 전환 전망, 원자재비 상승·자산손상 반영</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14161,19 +14463,19 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 톈수즈신(중국 AI 가속칩 설계): 알리바바 102억달러 유상증자發 AI 밸류체인 동반 급락, 10.6% 하락</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14211,15 +14513,19 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>밍밍헌망(중국 간식 소매체인): 특별한 뉴스 없음(수급 흐름 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14263,15 +14569,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>샤오펑(전기차): 2분기 인도량 증가율 0.1퍼센트로 컨센 하회, 급락</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14315,15 +14625,19 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>우시XDC(항체약물접합체 위탁생산): 실적 가이던스 상향·수주잔고 급증</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14367,7 +14681,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>니오(전기차): 샤오펑 실적 부진 여파로 전기차 업종 동반 약세</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N20"/>
@@ -14473,7 +14791,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14518,14 +14836,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 시노펙 A주(중국 최대 정유·화학): 상반기 순이익 19.3% 증가와 자사주매입 계획에 4.5% 상승</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14574,14 +14892,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) (AI 반도체 설계) 특별한 호재 부재, 차익실현과 수급 이탈 추정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14630,19 +14948,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 중신은행 A주(중국 상업은행): 기술주 급락 속 저평가·고배당 선호로 자금이동, 장중 사상최고가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14686,10 +15004,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>리쉰정밀(애플 공급망 정밀부품): 장중 신저 후 반등 마감, 개별 촉매 미확인</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14734,10 +15056,10 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14786,19 +15108,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 위수커지(사족보행 로봇 제조): 상장 초기 차익실현 급증, 시초가 대비 45% 넘게 반락</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14842,15 +15164,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>마이루이의료(의료기기): 특별한 뉴스 없음, 의료기기 섹터 수급 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14896,10 +15222,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>쑹파세라믹(도자기 식기): 특별한 뉴스 없음, 소형 테마주 수급 쏠림 추정</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14948,19 +15278,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) (신재생에너지 발전 자회사) 특별한 뉴스 없음, 전력 유틸리티 업종 약세 동반</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15004,10 +15334,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>헝리유압(굴착기용 유압부품): 특별한 뉴스 없음, 건설기계 섹터 조정 흐름 추정</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15060,14 +15394,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 웨이얼반도체(카메라용 이미지센서 설계): 알리바바 유상증자發 기술주 약세와 금리 상승 여파로 조정</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15114,10 +15448,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15162,14 +15496,14 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>(전일) 베리실리콘(반도체 설계자산·설계서비스): 금리 상승과 AI 밸류 부담에 반도체 설계주 동반 하락</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15218,7 +15552,7 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>(전일) 저장신허(비타민·정밀화학 생산): 개별 악재 미확인, 화학·성장주 동반 약세 추정</t>
         </is>
